--- a/preorder_forms/050_child_warmer_preorder_form--preorder_forms.xlsx
+++ b/preorder_forms/050_child_warmer_preorder_form--preorder_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -835,8 +835,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -864,12 +864,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'model_a_-_standard_edition',_'value':_'standard'}</t>
+          <t>model_a_-_standard_edition</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Model A - Standard Edition', 'value': 'standard'}</t>
+          <t>Model A - Standard Edition</t>
         </is>
       </c>
     </row>
@@ -881,12 +881,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'model_b_-_deluxe_comfort',_'value':_'deluxe'}</t>
+          <t>model_b_-_deluxe_comfort</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Model B - Deluxe Comfort', 'value': 'deluxe'}</t>
+          <t>Model B - Deluxe Comfort</t>
         </is>
       </c>
     </row>
@@ -898,12 +898,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'model_c_-_portable_travel',_'value':_'portable'}</t>
+          <t>model_c_-_portable_travel</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Model C - Portable Travel', 'value': 'portable'}</t>
+          <t>Model C - Portable Travel</t>
         </is>
       </c>
     </row>
@@ -915,12 +915,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'soft_blue',_'value':_'blue'}</t>
+          <t>soft_blue</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Soft Blue', 'value': 'blue'}</t>
+          <t>Soft Blue</t>
         </is>
       </c>
     </row>
@@ -932,12 +932,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'rose_pink',_'value':_'pink'}</t>
+          <t>rose_pink</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Rose Pink', 'value': 'pink'}</t>
+          <t>Rose Pink</t>
         </is>
       </c>
     </row>
@@ -949,12 +949,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'cloud_grey',_'value':_'grey'}</t>
+          <t>cloud_grey</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Cloud Grey', 'value': 'grey'}</t>
+          <t>Cloud Grey</t>
         </is>
       </c>
     </row>
@@ -966,12 +966,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'sage_green',_'value':_'green'}</t>
+          <t>sage_green</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Sage Green', 'value': 'green'}</t>
+          <t>Sage Green</t>
         </is>
       </c>
     </row>
